--- a/docs/evidence/Silent_Flyway_Data_Provenance.xlsx
+++ b/docs/evidence/Silent_Flyway_Data_Provenance.xlsx
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Mai Po, 20 Oct 2002 - highest count since 1999</t>
+          <t>Long Valley, 10 Oct 2001; carried as the standing record in every Bird Report header from 2007 to 2013 as 'highest count since 1999, 150 on 10 October 2001'</t>
         </is>
       </c>
     </row>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>2014</v>
+        <v>2002</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -844,30 +844,30 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Long Valley, 10 Nov 2014 - next highest since 1999</t>
+          <t>Mai Po, 20 Oct 2002. PROVENANCE WORTH KNOWING: the 2002 Bird Report records this as one observer's estimate and EXCLUDED it from that month's bird-day total, yet later reports and the avifauna account both adopt it as the standing record since 1999. Kept as documented because HKBWS itself treats it as the record, but it is an estimate, not a systematic count</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Eurasian Coot</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Fulica atra</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1971</v>
+        <v>2003</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>450</v>
+        <v>20</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
+          <t>peak passage count</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -877,35 +877,35 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0060/007800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>winter 1970/71, highest in that winter being 450 in January</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Eurasian Coot</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Fulica atra</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1972</v>
+        <v>2004</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2600</v>
+        <v>75</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
+          <t>peak passage count</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -915,73 +915,73 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0060/007800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>2,600 present in early February 1972</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Eurasian Coot</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Fulica atra</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1984</v>
+        <v>2005</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1200</v>
+        <v>12</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+          <t>peak passage count</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0060/007800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>SOURCE GIVES A RANGE, NOT A YEAR: 'from winter 1983/84 until 1996/97 the peak winter count was often 1,200 or more'. Pinning it to 1984 is a convention, not a count</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Eurasian Coot</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Fulica atra</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1992</v>
+        <v>2006</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>3245</v>
+        <v>15</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
+          <t>peak passage count</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -991,35 +991,35 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0060/007800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>highest being 3,245 on 12 January 1992</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Eurasian Coot</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Fulica atra</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
+          <t>peak passage count</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -1029,35 +1029,35 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0060/007800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>since winter 2011/12 the highest winter waterbird count is 66 - an upper bound across all later winters</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Northern Pintail</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>1997</v>
+        <v>2008</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>8651</v>
+        <v>25</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
+          <t>peak passage count</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1067,35 +1067,35 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0020/002300</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>highest WHOLE Deep Bay count, 8,651 on 15 February 1997</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Northern Pintail</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>2000</v>
+        <v>2009</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>8086</v>
+        <v>23</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
+          <t>peak passage count</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1105,73 +1105,73 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0020/002300</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>highest count on the HK SIDE of Deep Bay, 8,086 on 15 January 2000 - different spatial extent to the 1997 figure</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Northern Pintail</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Anas acuta</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>2000</v>
+        <v>20</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+          <t>peak passage count</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0020/002300</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>SOURCE GIVES AN UPPER BOUND: 'in the most recent three winter periods less than 2,000'. The true figure is below this</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Common Shelduck</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Tadorna tadorna</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1974</v>
+        <v>2011</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
+          <t>peak passage count</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1181,35 +1181,35 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>until the 1974-75 winter period the highest count was 115 - a maximum across all earlier years, not a single-year count</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Common Shelduck</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Tadorna tadorna</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1988</v>
+        <v>2012</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>4011</v>
+        <v>50</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
+          <t>peak passage count</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -1219,35 +1219,35 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>peak of 4,011 birds on 17 January 1988, the highest on record in HK</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Common Shelduck</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Tadorna tadorna</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1992</v>
+        <v>2013</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>387</v>
+        <v>20</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
+          <t>peak passage count</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -1257,35 +1257,35 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>sharp decline to 387 in winter 1991/92</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Common Shelduck</t>
+          <t>Yellow-breasted Bunting</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Tadorna tadorna</t>
+          <t>Emberiza aureola</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1997</v>
+        <v>2014</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2972</v>
+        <v>120</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>peak winter count</t>
+          <t>peak passage count</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -1295,31 +1295,31 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>peak count of 2,972 in winter 1996/97</t>
+          <t>annual peak count, autumn passage</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Common Shelduck</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Tadorna tadorna</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>2000</v>
+        <v>1971</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1300</v>
+        <v>450</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -1333,31 +1333,31 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+          <t>https://avifauna.hkbws.org.hk/species/0060/007800</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>the following three winter periods brought peak counts of approximately 1,300 birds - approximate as published</t>
+          <t>winter 1970/71, highest in that winter being 450 in January</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Common Shelduck</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Tadorna tadorna</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2008</v>
+        <v>1972</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>18</v>
+        <v>2600</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -1371,69 +1371,69 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+          <t>https://avifauna.hkbws.org.hk/species/0060/007800</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>sharp decrease to 18 in winter 2007-08</t>
+          <t>2,600 present in early February 1972</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Common Shelduck</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Tadorna tadorna</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>2013</v>
+        <v>1984</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>documented</t>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>estimated</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+          <t>https://avifauna.hkbws.org.hk/species/0060/007800</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>2012/13, one present until 2 March</t>
+          <t>SOURCE GIVES A RANGE, NOT A YEAR: 'from winter 1983/84 until 1996/97 the peak winter count was often 1,200 or more'. Pinning it to 1984 is a convention, not a count</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Common Shelduck</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Tadorna tadorna</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>2020</v>
+        <v>1992</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>3245</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -1447,31 +1447,31 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+          <t>https://avifauna.hkbws.org.hk/species/0060/007800</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>one on 26 February 2020, last seen 18 March - the final confirmed record</t>
+          <t>highest being 3,245 on 12 January 1992</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Dalmatian Pelican</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Pelecanus crispus</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>1960</v>
+        <v>1999</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>85</v>
+        <v>679</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -1485,107 +1485,107 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0170/023800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>peak count of 85 on 21 February 1960</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Dalmatian Pelican</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Pelecanus crispus</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1982</v>
+        <v>2000</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>38</v>
+        <v>654</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0170/023800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>SOURCE GIVES A RANGE ACROSS A DECADE: 'during the 1980s the five highest peak counts were much lower, in the range 26-38'. 38 is the upper bound, pinned to the 1981-82 watershed by convention</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Dalmatian Pelican</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Pelecanus crispus</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>10</v>
+        <v>534</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0170/023800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>SOURCE SAYS ONLY 'the last double-figure count occurred in winter 2004/05'. The true figure is 10 or more</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Dalmatian Pelican</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Pelecanus crispus</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -1599,31 +1599,31 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0170/023800</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>final record of one on 3 January 2010</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Black-headed Ibis</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Threskiornis melanocephalus</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1973</v>
+        <v>2003</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -1637,31 +1637,31 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0160/021600</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>18 on 8 April 1973</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Black-headed Ibis</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Threskiornis melanocephalus</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1974</v>
+        <v>2004</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>25</v>
+        <v>260</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -1675,31 +1675,31 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0160/021600</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>25 on 6 January 1974 - the highest count on record</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Black-headed Ibis</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Threskiornis melanocephalus</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -1713,297 +1713,297 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0160/021600</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>the final record, 27 November 1999</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1994</v>
+        <v>2006</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>86</v>
+        <v>378</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>first International Synchronous BFS Census; individual year not yet checked against the census report</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1996</v>
+        <v>2007</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>124</v>
+        <v>620</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>individual year not yet checked</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>152</v>
+        <v>728</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>individual year not yet checked</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>2000</v>
+        <v>2009</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>199</v>
+        <v>325</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>individual year not yet checked</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>2003</v>
+        <v>2010</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>258</v>
+        <v>354</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>individual year not yet checked</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>2005</v>
+        <v>2011</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>316</v>
+        <v>125</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>individual year not yet checked</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>374</v>
+        <v>9</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>individual year not yet checked</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>462</v>
+        <v>31</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
@@ -2017,31 +2017,31 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-2024-en</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>the all-time Deep Bay high; HKBWS describes an all-time high of 462 in 2010</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Eurasian Coot</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Fulica atra</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>411</v>
+        <v>48</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -2055,145 +2055,145 @@
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-2024-en</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>cross-checked by ratio: the 2024 report says Deep Bay held 'over 20%' of the world population in 2011, and 411 of a 1,848 global total is 22.2%</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>2013</v>
+        <v>1997</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>351</v>
+        <v>8651</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>https://avifauna.hkbws.org.hk/species/0020/002300</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>individual year not yet checked</t>
+          <t>highest WHOLE Deep Bay count, 8,651 on 15 February 1997</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>2015</v>
+        <v>1999</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>411</v>
+        <v>5646</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>individual year not yet checked; a candidate referent for the 2026 report's 'peak of 411 ten years ago'</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>2016</v>
+        <v>2000</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>371</v>
+        <v>8086</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>independently given as 371 by a second research pass, which raises confidence, but neither cited the census report itself</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>375</v>
+        <v>3435</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -2207,31 +2207,31 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>https://www.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census2019en</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Hong Kong &amp; Shenzhen (Deep Bay), 375, being 9.5% of the global total</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>2018</v>
+        <v>2002</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>350</v>
+        <v>2609</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
@@ -2245,31 +2245,31 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>https://www.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census2019en</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Deep Bay 350, 8.9% of the global total</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>2019</v>
+        <v>2003</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>383</v>
+        <v>4381</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
@@ -2283,107 +2283,107 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>https://www.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census2019en</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Deep Bay 383, 8.6% of the global total</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>2021</v>
+        <v>2004</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>336</v>
+        <v>2054</v>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>individual year not yet checked</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>2022</v>
+        <v>2005</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>369</v>
+        <v>3332</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
           <t>peak winter count</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>secondary</t>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>compiled series, Kimi 2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>individual year not yet checked</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>2023</v>
+        <v>2006</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>299</v>
+        <v>1556</v>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
@@ -2397,31 +2397,31 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-2024-en</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>derived by arithmetic from the 2024 report: 375 was 'a growth of 25.4%', giving 299. A compiled series states 299 independently</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>2024</v>
+        <v>2007</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>375</v>
+        <v>4647</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
@@ -2435,31 +2435,31 @@
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-2024-en</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Deep Bay 375 of a global 6,988, the second lowest share in history at 5.4%</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>2025</v>
+        <v>2008</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>328</v>
+        <v>2444</v>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
@@ -2473,31 +2473,31 @@
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-en-2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>derived by arithmetic from the 2026 report: 341 was 'an increase of 13 individuals' on the previous year</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Black-faced Spoonbill</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Platalea minor</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>2026</v>
+        <v>2009</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>341</v>
+        <v>2010</v>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
@@ -2511,35 +2511,35 @@
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-en-2026</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>Deep Bay recorded 341 individuals, a 4.0% increase; share a historic low of 4.4%</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Black-capped Kingfisher</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Halcyon pileata</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C52" s="5" t="n">
-        <v>2001</v>
+        <v>2010</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>8</v>
+        <v>3622</v>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>mean winter count</t>
+          <t>peak winter count</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -2549,35 +2549,35 @@
       </c>
       <c r="G52" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0200/028100</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>mean peak count across the six winters 1998/99 to 2003/04; pinned to the period midpoint</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Black-capped Kingfisher</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Halcyon pileata</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C53" s="5" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>1.6</v>
+        <v>2586</v>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>mean winter count</t>
+          <t>peak winter count</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
@@ -2587,35 +2587,35 @@
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0200/028100</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>mean peak count across the six winters 2015/16 to 2020/21; pinned to the period midpoint</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>White-throated Kingfisher</t>
+          <t>Northern Pintail</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Halcyon smyrnensis</t>
+          <t>Anas acuta</t>
         </is>
       </c>
       <c r="C54" s="5" t="n">
-        <v>1994</v>
+        <v>2012</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>7.3</v>
+        <v>2413</v>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>atlas occupancy</t>
+          <t>peak winter count</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -2625,57 +2625,3135 @@
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>https://avifauna.hkbws.org.hk/species/0200/028300</t>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>breeding atlas 1993-96, 7.3% of 1km squares occupied; pinned to the period midpoint</t>
+          <t>Deep Bay waterbird count annual peak</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
+          <t>Northern Pintail</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Anas acuta</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>1748</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Northern Pintail</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Anas acuta</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>1410</v>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Northern Pintail</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Anas acuta</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0020/002300</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>SOURCE GIVES AN UPPER BOUND: 'in the most recent three winter periods less than 2,000'. The true figure is below this</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>1974</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>until the 1974-75 winter period the highest count was 115 - a maximum across all earlier years, not a single-year count</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>4011</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>peak of 4,011 birds on 17 January 1988, the highest on record in HK</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>1992</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>387</v>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>sharp decline to 387 in winter 1991/92</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>1997</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>2972</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>peak count of 2,972 in winter 1996/97</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>1999</v>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>1320</v>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>373</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Common Shelduck</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Tadorna tadorna</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0010/000800</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>one on 26 February 2020, last seen 18 March - the final confirmed record</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Dalmatian Pelican</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Pelecanus crispus</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="n">
+        <v>1960</v>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0170/023800</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>peak count of 85 on 21 February 1960</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Dalmatian Pelican</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Pelecanus crispus</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="n">
+        <v>1982</v>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0170/023800</t>
+        </is>
+      </c>
+      <c r="H80" s="7" t="inlineStr">
+        <is>
+          <t>SOURCE GIVES A RANGE ACROSS A DECADE: 'during the 1980s the five highest peak counts were much lower, in the range 26-38'. 38 is the upper bound, pinned to the 1981-82 watershed by convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Dalmatian Pelican</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Pelecanus crispus</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>estimated</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0170/023800</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>SOURCE SAYS ONLY 'the last double-figure count occurred in winter 2004/05'. The true figure is 10 or more</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Dalmatian Pelican</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Pelecanus crispus</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0170/023800</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>final record of one on 3 January 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Black-headed Ibis</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Threskiornis melanocephalus</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>1973</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0160/021600</t>
+        </is>
+      </c>
+      <c r="H83" s="7" t="inlineStr">
+        <is>
+          <t>18 on 8 April 1973</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Black-headed Ibis</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Threskiornis melanocephalus</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>1974</v>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0160/021600</t>
+        </is>
+      </c>
+      <c r="H84" s="7" t="inlineStr">
+        <is>
+          <t>25 on 6 January 1974 - the highest count on record</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Black-headed Ibis</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Threskiornis melanocephalus</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="n">
+        <v>1999</v>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>https://avifauna.hkbws.org.hk/species/0160/021600</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>the final record, 27 November 1999</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="n">
+        <v>1994</v>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>first International Synchronous BFS Census; individual year not yet checked against the census report</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="n">
+        <v>1996</v>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>individual year not yet checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="n">
+        <v>1998</v>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
+          <t>individual year not yet checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>199</v>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>individual year not yet checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>individual year not yet checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>316</v>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>individual year not yet checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>374</v>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>individual year not yet checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>462</v>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-2024-en</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>the all-time Deep Bay high; HKBWS describes an all-time high of 462 in 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>411</v>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-2024-en</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>cross-checked by ratio: the 2024 report says Deep Bay held 'over 20%' of the world population in 2011, and 411 of a 1,848 global total is 22.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>351</v>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>individual year not yet checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>411</v>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>individual year not yet checked; a candidate referent for the 2026 report's 'peak of 411 ten years ago'</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>371</v>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>independently given as 371 by a second research pass, which raises confidence, but neither cited the census report itself</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census2019en</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong &amp; Shenzhen (Deep Bay), 375, being 9.5% of the global total</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census2019en</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay 350, 8.9% of the global total</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>383</v>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>https://www.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census2019en</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay 383, 8.6% of the global total</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>336</v>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>individual year not yet checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>369</v>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>compiled series, Kimi 2026</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>individual year not yet checked</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>299</v>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-2024-en</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>derived by arithmetic from the 2024 report: 375 was 'a growth of 25.4%', giving 299. A compiled series states 299 independently</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-2024-en</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay 375 of a global 6,988, the second lowest share in history at 5.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>328</v>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-en-2026</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>derived by arithmetic from the 2026 report: 341 was 'an increase of 13 individuals' on the previous year</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Black-faced Spoonbill</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Platalea minor</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>341</v>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>https://cms.hkbws.org.hk/cms/en/hkbws/work/endangered-species/bfs-en/bfs-census-en-2026</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay recorded 341 individuals, a 4.0% increase; share a historic low of 4.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H112" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H113" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H118" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>Black-capped Kingfisher</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon pileata</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H121" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
           <t>White-throated Kingfisher</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B122" s="5" t="inlineStr">
         <is>
           <t>Halcyon smyrnensis</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
-        <v>2017</v>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>atlas occupancy</t>
-        </is>
-      </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>documented</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>https://avifauna.hkbws.org.hk/species/0200/028300</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>breeding atlas 2016-19, 3.0% of 1km squares occupied; pinned to the period midpoint</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>documented 36   ·   secondary 12   ·   estimated 4</t>
+      <c r="C122" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H122" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H123" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="n">
+        <v>2003</v>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H125" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>2004</v>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H126" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="n">
+        <v>2005</v>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H127" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="n">
+        <v>2006</v>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>2011</v>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>White-throated Kingfisher</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Halcyon smyrnensis</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>peak winter count</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>Hong Kong Bird Report, HKBWS - 'Peak counts by year' tables, cross-checked across overlapping report windows</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>Deep Bay waterbird count annual peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>documented 117   ·   secondary 12   ·   estimated 4</t>
         </is>
       </c>
     </row>
@@ -2851,10 +5929,10 @@
         <v>86</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
@@ -2928,10 +6006,10 @@
         <v>86</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
@@ -3005,10 +6083,10 @@
         <v>86</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
@@ -3082,10 +6160,10 @@
         <v>86</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
@@ -3159,10 +6237,10 @@
         <v>86</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
@@ -3236,10 +6314,10 @@
         <v>86</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
@@ -3313,10 +6391,10 @@
         <v>86</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
@@ -3390,10 +6468,10 @@
         <v>86</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
@@ -3467,10 +6545,10 @@
         <v>86</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
@@ -3544,10 +6622,10 @@
         <v>86</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
@@ -3621,10 +6699,10 @@
         <v>86</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -3698,10 +6776,10 @@
         <v>86</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
@@ -3775,10 +6853,10 @@
         <v>86</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
@@ -3852,10 +6930,10 @@
         <v>86</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
@@ -3929,10 +7007,10 @@
         <v>86</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
@@ -4006,10 +7084,10 @@
         <v>86</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -4083,10 +7161,10 @@
         <v>86</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
@@ -4160,10 +7238,10 @@
         <v>86</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
@@ -4237,10 +7315,10 @@
         <v>86</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
@@ -4314,10 +7392,10 @@
         <v>86</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
@@ -4391,10 +7469,10 @@
         <v>86</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
@@ -4468,10 +7546,10 @@
         <v>86</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
@@ -4545,10 +7623,10 @@
         <v>86</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
@@ -4622,10 +7700,10 @@
         <v>86</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
@@ -4699,10 +7777,10 @@
         <v>86</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
@@ -4776,10 +7854,10 @@
         <v>86</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
@@ -4853,10 +7931,10 @@
         <v>86</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
@@ -4930,10 +8008,10 @@
         <v>86</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
@@ -5007,10 +8085,10 @@
         <v>86</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
@@ -5084,10 +8162,10 @@
         <v>86</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
@@ -5161,10 +8239,10 @@
         <v>86</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
@@ -5238,10 +8316,10 @@
         <v>86</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
@@ -5315,10 +8393,10 @@
         <v>86</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
@@ -5392,10 +8470,10 @@
         <v>86</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
@@ -5451,7 +8529,7 @@
         <v>615.7</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>3222</v>
+        <v>3102.9</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>8651</v>
@@ -5469,10 +8547,10 @@
         <v>86</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
@@ -5528,7 +8606,7 @@
         <v>610</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>3156</v>
+        <v>2736.3</v>
       </c>
       <c r="D40" s="5" t="n">
         <v>8651</v>
@@ -5546,10 +8624,10 @@
         <v>86</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
@@ -5602,10 +8680,10 @@
         <v>1995</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>596.7</v>
+        <v>584.5</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>3051.9</v>
+        <v>2235.1</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>8651</v>
@@ -5623,10 +8701,10 @@
         <v>105</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
@@ -5679,10 +8757,10 @@
         <v>1996</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>561.6</v>
+        <v>518.8</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>2914.4</v>
+        <v>1688.9</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>8651</v>
@@ -5700,10 +8778,10 @@
         <v>124</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>7.2</v>
+        <v>46</v>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
@@ -5756,10 +8834,10 @@
         <v>1997</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>511.9</v>
+        <v>429</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>2748.3</v>
+        <v>1187.7</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>8651</v>
@@ -5777,10 +8855,10 @@
         <v>138</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>7.1</v>
+        <v>46</v>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
@@ -5833,16 +8911,16 @@
         <v>1998</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>455</v>
+        <v>331</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>2558.3</v>
+        <v>821.1</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>8504.5</v>
+        <v>7148.5</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2538.5</v>
+        <v>2111</v>
       </c>
       <c r="F44" s="5" t="n">
         <v>15.1</v>
@@ -5854,10 +8932,10 @@
         <v>152</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
@@ -5910,16 +8988,16 @@
         <v>1999</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>398.1</v>
+        <v>241.2</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>2349.3</v>
+        <v>679</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>8232.5</v>
+        <v>5646</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1733.5</v>
+        <v>1250</v>
       </c>
       <c r="F45" s="5" t="n">
         <v>13.7</v>
@@ -5931,10 +9009,10 @@
         <v>175.5</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>6.8</v>
+        <v>46</v>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
@@ -5987,16 +9065,16 @@
         <v>2000</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>348.4</v>
+        <v>175.5</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>2126</v>
+        <v>654</v>
       </c>
       <c r="D46" s="5" t="n">
         <v>8086</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1300</v>
+        <v>1320</v>
       </c>
       <c r="F46" s="5" t="n">
         <v>12.4</v>
@@ -6010,10 +9088,10 @@
         <v>199</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>6.6</v>
+        <v>46</v>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
@@ -6066,16 +9144,16 @@
         <v>2001</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>313.3</v>
+        <v>150</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1893.1</v>
+        <v>534</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>8041.9</v>
+        <v>3435</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1244.9</v>
+        <v>373</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>11.4</v>
@@ -6092,7 +9170,7 @@
         <v>8</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>6.3</v>
+        <v>31</v>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
@@ -6104,9 +9182,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M47" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -6148,13 +9226,13 @@
         <v>300</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>1655.5</v>
+        <v>179</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>7915.6</v>
+        <v>2609</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1099.7</v>
+        <v>268</v>
       </c>
       <c r="F48" s="5" t="n">
         <v>10.7</v>
@@ -6168,10 +9246,10 @@
         <v>242.7</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>7.9</v>
+        <v>17</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>6.1</v>
+        <v>44</v>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
@@ -6183,9 +9261,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M48" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N48" s="6" t="inlineStr">
@@ -6224,16 +9302,16 @@
         <v>2003</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>296.5</v>
+        <v>20</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1417.9</v>
+        <v>42</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>7716.3</v>
+        <v>4381</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>894.4</v>
+        <v>192</v>
       </c>
       <c r="F49" s="5" t="n">
         <v>10.2</v>
@@ -6247,10 +9325,10 @@
         <v>258</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>5.8</v>
+        <v>35</v>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
@@ -6262,9 +9340,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M49" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N49" s="6" t="inlineStr">
@@ -6303,16 +9381,16 @@
         <v>2004</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>286.7</v>
+        <v>75</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>1185</v>
+        <v>260</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>7453.1</v>
+        <v>2054</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>659</v>
+        <v>240</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>10</v>
@@ -6326,10 +9404,10 @@
         <v>287</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>7.5</v>
+        <v>11</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>5.6</v>
+        <v>39</v>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
@@ -6341,9 +9419,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M50" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N50" s="6" t="inlineStr">
@@ -6382,16 +9460,16 @@
         <v>2005</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>271.9</v>
+        <v>12</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>961.7</v>
+        <v>317</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>7135.1</v>
+        <v>3332</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>423.6</v>
+        <v>68</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>9.300000000000001</v>
@@ -6405,10 +9483,10 @@
         <v>316</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>5.3</v>
+        <v>46</v>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
@@ -6420,9 +9498,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M51" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N51" s="6" t="inlineStr">
@@ -6461,16 +9539,16 @@
         <v>2006</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>253.3</v>
+        <v>15</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>752.7</v>
+        <v>378</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>6771.4</v>
+        <v>1556</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>218.3</v>
+        <v>60</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>7.7</v>
@@ -6484,10 +9562,10 @@
         <v>331</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>6.7</v>
+        <v>13</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
@@ -6499,9 +9577,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M52" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N52" s="6" t="inlineStr">
@@ -6540,16 +9618,16 @@
         <v>2007</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>232.3</v>
+        <v>25</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>562.7</v>
+        <v>620</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>6371.3</v>
+        <v>4647</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>73.09999999999999</v>
+        <v>44</v>
       </c>
       <c r="F53" s="5" t="n">
         <v>5.5</v>
@@ -6563,10 +9641,10 @@
         <v>359</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>4.7</v>
+        <v>33</v>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
@@ -6578,9 +9656,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M53" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N53" s="6" t="inlineStr">
@@ -6619,16 +9697,16 @@
         <v>2008</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>396.6</v>
+        <v>728</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>5943.7</v>
+        <v>2444</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F54" s="5" t="n">
         <v>3.3</v>
@@ -6642,10 +9720,10 @@
         <v>374</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>4.5</v>
+        <v>43</v>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
@@ -6657,9 +9735,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M54" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N54" s="6" t="inlineStr">
@@ -6698,16 +9776,16 @@
         <v>2009</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>187.7</v>
+        <v>23</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>259.1</v>
+        <v>325</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>5497.9</v>
+        <v>2010</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>16.2</v>
+        <v>9</v>
       </c>
       <c r="F55" s="5" t="n">
         <v>1.7</v>
@@ -6721,10 +9799,10 @@
         <v>418</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
@@ -6736,9 +9814,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M55" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N55" s="6" t="inlineStr">
@@ -6777,16 +9855,16 @@
         <v>2010</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>166.7</v>
+        <v>20</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>155</v>
+        <v>354</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>5043</v>
+        <v>3622</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>1</v>
@@ -6800,10 +9878,10 @@
         <v>462</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
@@ -6815,9 +9893,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M56" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N56" s="6" t="inlineStr">
@@ -6856,16 +9934,16 @@
         <v>2011</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>148.1</v>
+        <v>20</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>4588.1</v>
+        <v>2586</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
@@ -6881,10 +9959,10 @@
         <v>411</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>3.7</v>
+        <v>26</v>
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
@@ -6896,9 +9974,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M57" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N57" s="6" t="inlineStr">
@@ -6937,16 +10015,16 @@
         <v>2012</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>133.3</v>
+        <v>50</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>4142.3</v>
+        <v>2413</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
@@ -6962,10 +10040,10 @@
         <v>381</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>3.5</v>
+        <v>22</v>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
@@ -6977,9 +10055,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M58" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N58" s="6" t="inlineStr">
@@ -7018,13 +10096,13 @@
         <v>2013</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>123.5</v>
+        <v>20</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>3714.7</v>
+        <v>1748</v>
       </c>
       <c r="E59" s="5" t="n">
         <v>1</v>
@@ -7043,10 +10121,10 @@
         <v>351</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>3.3</v>
+        <v>23</v>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
@@ -7058,9 +10136,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M59" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N59" s="6" t="inlineStr">
@@ -7102,13 +10180,13 @@
         <v>120</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>3314.6</v>
+        <v>1410</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
@@ -7124,10 +10202,10 @@
         <v>381</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>3.2</v>
+        <v>23</v>
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
@@ -7139,9 +10217,9 @@
           <t>documented</t>
         </is>
       </c>
-      <c r="M60" s="8" t="inlineStr">
-        <is>
-          <t>estimated</t>
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t>documented</t>
         </is>
       </c>
       <c r="N60" s="6" t="inlineStr">
@@ -7183,13 +10261,13 @@
         <v>120</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>2950.9</v>
+        <v>1453.7</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
@@ -7205,10 +10283,10 @@
         <v>411</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>3.1</v>
+        <v>23</v>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
@@ -7264,13 +10342,13 @@
         <v>120</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>2632.9</v>
+        <v>1563</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -7286,10 +10364,10 @@
         <v>371</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
@@ -7345,13 +10423,13 @@
         <v>120</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>2369.7</v>
+        <v>1705</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -7367,10 +10445,10 @@
         <v>375</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
@@ -7426,13 +10504,13 @@
         <v>120</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>2170.4</v>
+        <v>1847</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -7448,10 +10526,10 @@
         <v>350</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
@@ -7507,13 +10585,13 @@
         <v>120</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>2044.1</v>
+        <v>1956.3</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
@@ -7529,10 +10607,10 @@
         <v>383</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
@@ -7588,7 +10666,7 @@
         <v>120</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D66" s="5" t="n">
         <v>2000</v>
@@ -7610,10 +10688,10 @@
         <v>359.5</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
@@ -7669,7 +10747,7 @@
         <v>120</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D67" s="5" t="n">
         <v>2000</v>
@@ -7693,10 +10771,10 @@
         <v>336</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
@@ -7752,7 +10830,7 @@
         <v>120</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D68" s="5" t="n">
         <v>2000</v>
@@ -7776,10 +10854,10 @@
         <v>369</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
@@ -7835,7 +10913,7 @@
         <v>120</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D69" s="5" t="n">
         <v>2000</v>
@@ -7859,10 +10937,10 @@
         <v>299</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
@@ -7918,7 +10996,7 @@
         <v>120</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D70" s="5" t="n">
         <v>2000</v>
@@ -7942,10 +11020,10 @@
         <v>375</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
@@ -8001,7 +11079,7 @@
         <v>120</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D71" s="5" t="n">
         <v>2000</v>
@@ -8025,10 +11103,10 @@
         <v>328</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
@@ -8084,7 +11162,7 @@
         <v>120</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D72" s="5" t="n">
         <v>2000</v>
@@ -8108,10 +11186,10 @@
         <v>341</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
@@ -9342,10 +12420,10 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>1959</v>
@@ -9397,22 +12475,22 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G5" s="5" t="n">
         <v>1971</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>3245</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
@@ -9452,10 +12530,10 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1997</v>
@@ -9507,10 +12585,10 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>1974</v>
@@ -9717,26 +12795,26 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>mean winter count</t>
+          <t>peak winter count</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
@@ -9772,26 +12850,26 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>atlas occupancy</t>
+          <t>peak winter count</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1994</v>
+        <v>2000</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>7.3</v>
+        <v>46</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>

--- a/docs/evidence/Silent_Flyway_Data_Provenance.xlsx
+++ b/docs/evidence/Silent_Flyway_Data_Provenance.xlsx
@@ -12059,7 +12059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12292,6 +12292,138 @@
       <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Returned with no source URLs at all, despite the sourcing requirement. Not rejected as false - several items later proved correct - but nothing from it was allowed into the data on its own authority. Each item was treated as a lead and checked independently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Black Drongo declined about 90% (1,000 to 101)</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>My own ranking of 168 Bird Report peak-count tables by first-to-last value</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>A ranking cannot see a spike. HKBWS states: 'peak counts are higher than in the 1990s with an exceptional count in 2010'. The apparent collapse is the 2010 outlier falling out of the window. Not a decliner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Red-billed Starling declined about 81% (11,260 to 2,184)</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Same ranking</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>HKBWS states: 'relatively stable since the 1990s except for exceptionally high numbers in the winter of 2006-07'. Same spike artefact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Chestnut Bulbul declined about 70%</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Same ranking</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>HKBWS lists it among 'species which have increased substantially in numbers since the 1990s and before'. The trend is the opposite of the ranking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Great Crested Grebe declined about 62%</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Same ranking</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>HKBWS states it 'was increasing in numbers up to 2012'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Blue-tailed Bee-eater declined about 64%</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Same ranking</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>HKBWS states it 'is now recorded in higher numbers than in the 1990s, mostly at MPNR'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Eurasian Skylark and Greater Painted-snipe as decline candidates</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Same ranking</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>HKBWS states Skylark 'has increased substantially' and Painted-snipe peak counts are 'relatively stable since 1994'.</t>
         </is>
       </c>
     </row>
